--- a/artfynd/A 26957-2024 artfynd.xlsx
+++ b/artfynd/A 26957-2024 artfynd.xlsx
@@ -1508,7 +1508,7 @@
         <v>128108775</v>
       </c>
       <c r="B10" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>128108776</v>
       </c>
       <c r="B11" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>128108777</v>
       </c>
       <c r="B14" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 26957-2024 artfynd.xlsx
+++ b/artfynd/A 26957-2024 artfynd.xlsx
@@ -1408,10 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128108782</v>
+        <v>128108775</v>
       </c>
       <c r="B9" t="n">
-        <v>82870</v>
+        <v>91346</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1419,21 +1419,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493906</v>
+        <v>493958</v>
       </c>
       <c r="R9" t="n">
-        <v>6933571</v>
+        <v>6933370</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128108775</v>
+        <v>128108782</v>
       </c>
       <c r="B10" t="n">
-        <v>91346</v>
+        <v>82870</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493958</v>
+        <v>493906</v>
       </c>
       <c r="R10" t="n">
-        <v>6933370</v>
+        <v>6933571</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>

--- a/artfynd/A 26957-2024 artfynd.xlsx
+++ b/artfynd/A 26957-2024 artfynd.xlsx
@@ -1408,10 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128108775</v>
+        <v>128108782</v>
       </c>
       <c r="B9" t="n">
-        <v>91346</v>
+        <v>82870</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1419,21 +1419,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493958</v>
+        <v>493906</v>
       </c>
       <c r="R9" t="n">
-        <v>6933370</v>
+        <v>6933571</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128108782</v>
+        <v>128108775</v>
       </c>
       <c r="B10" t="n">
-        <v>82870</v>
+        <v>91347</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493906</v>
+        <v>493958</v>
       </c>
       <c r="R10" t="n">
-        <v>6933571</v>
+        <v>6933370</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1605,7 +1605,7 @@
         <v>128108776</v>
       </c>
       <c r="B11" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>128108777</v>
       </c>
       <c r="B14" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 26957-2024 artfynd.xlsx
+++ b/artfynd/A 26957-2024 artfynd.xlsx
@@ -1408,10 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128108782</v>
+        <v>128108775</v>
       </c>
       <c r="B9" t="n">
-        <v>82870</v>
+        <v>91348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1419,21 +1419,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493906</v>
+        <v>493958</v>
       </c>
       <c r="R9" t="n">
-        <v>6933571</v>
+        <v>6933370</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128108775</v>
+        <v>128108782</v>
       </c>
       <c r="B10" t="n">
-        <v>91347</v>
+        <v>82870</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493958</v>
+        <v>493906</v>
       </c>
       <c r="R10" t="n">
-        <v>6933370</v>
+        <v>6933571</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1605,7 +1605,7 @@
         <v>128108776</v>
       </c>
       <c r="B11" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>128108777</v>
       </c>
       <c r="B14" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 26957-2024 artfynd.xlsx
+++ b/artfynd/A 26957-2024 artfynd.xlsx
@@ -1408,10 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128108775</v>
+        <v>128108782</v>
       </c>
       <c r="B9" t="n">
-        <v>91348</v>
+        <v>82870</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1419,21 +1419,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493958</v>
+        <v>493906</v>
       </c>
       <c r="R9" t="n">
-        <v>6933370</v>
+        <v>6933571</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128108782</v>
+        <v>128108775</v>
       </c>
       <c r="B10" t="n">
-        <v>82870</v>
+        <v>91348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493906</v>
+        <v>493958</v>
       </c>
       <c r="R10" t="n">
-        <v>6933571</v>
+        <v>6933370</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>

--- a/artfynd/A 26957-2024 artfynd.xlsx
+++ b/artfynd/A 26957-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128108769</v>
       </c>
       <c r="B2" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128103036</v>
       </c>
       <c r="B3" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>128102162</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>128108770</v>
       </c>
       <c r="B5" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>128102380</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>128108766</v>
       </c>
       <c r="B8" t="n">
-        <v>80133</v>
+        <v>80136</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>128108782</v>
       </c>
       <c r="B9" t="n">
-        <v>82870</v>
+        <v>82873</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>128108775</v>
       </c>
       <c r="B10" t="n">
-        <v>91348</v>
+        <v>91356</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>128108776</v>
       </c>
       <c r="B11" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>128108778</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>128108781</v>
       </c>
       <c r="B13" t="n">
-        <v>82870</v>
+        <v>82873</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>128108777</v>
       </c>
       <c r="B14" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 26957-2024 artfynd.xlsx
+++ b/artfynd/A 26957-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128108769</v>
       </c>
       <c r="B2" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128103036</v>
       </c>
       <c r="B3" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>128102162</v>
       </c>
       <c r="B4" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>128108770</v>
       </c>
       <c r="B5" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>128102380</v>
       </c>
       <c r="B6" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>128108766</v>
       </c>
       <c r="B8" t="n">
-        <v>80136</v>
+        <v>80189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,10 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128108782</v>
+        <v>128108775</v>
       </c>
       <c r="B9" t="n">
-        <v>82873</v>
+        <v>91448</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1419,21 +1419,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493906</v>
+        <v>493958</v>
       </c>
       <c r="R9" t="n">
-        <v>6933571</v>
+        <v>6933370</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128108775</v>
+        <v>128108782</v>
       </c>
       <c r="B10" t="n">
-        <v>91356</v>
+        <v>82942</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493958</v>
+        <v>493906</v>
       </c>
       <c r="R10" t="n">
-        <v>6933370</v>
+        <v>6933571</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1605,7 +1605,7 @@
         <v>128108776</v>
       </c>
       <c r="B11" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>128108778</v>
       </c>
       <c r="B12" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>128108781</v>
       </c>
       <c r="B13" t="n">
-        <v>82873</v>
+        <v>82942</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>128108777</v>
       </c>
       <c r="B14" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 26957-2024 artfynd.xlsx
+++ b/artfynd/A 26957-2024 artfynd.xlsx
@@ -1408,10 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128108775</v>
+        <v>128108782</v>
       </c>
       <c r="B9" t="n">
-        <v>91448</v>
+        <v>82942</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1419,21 +1419,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493958</v>
+        <v>493906</v>
       </c>
       <c r="R9" t="n">
-        <v>6933370</v>
+        <v>6933571</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128108782</v>
+        <v>128108775</v>
       </c>
       <c r="B10" t="n">
-        <v>82942</v>
+        <v>91448</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493906</v>
+        <v>493958</v>
       </c>
       <c r="R10" t="n">
-        <v>6933571</v>
+        <v>6933370</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>

--- a/artfynd/A 26957-2024 artfynd.xlsx
+++ b/artfynd/A 26957-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128108769</v>
       </c>
       <c r="B2" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128103036</v>
       </c>
       <c r="B3" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>128102162</v>
       </c>
       <c r="B4" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>128108770</v>
       </c>
       <c r="B5" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>128102380</v>
       </c>
       <c r="B6" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>128108766</v>
       </c>
       <c r="B8" t="n">
-        <v>80189</v>
+        <v>80193</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>128108782</v>
       </c>
       <c r="B9" t="n">
-        <v>82942</v>
+        <v>82946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>128108775</v>
       </c>
       <c r="B10" t="n">
-        <v>91448</v>
+        <v>91460</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>128108776</v>
       </c>
       <c r="B11" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>128108778</v>
       </c>
       <c r="B12" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>128108781</v>
       </c>
       <c r="B13" t="n">
-        <v>82942</v>
+        <v>82946</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>128108777</v>
       </c>
       <c r="B14" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 26957-2024 artfynd.xlsx
+++ b/artfynd/A 26957-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128108769</v>
       </c>
       <c r="B2" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>128102162</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>128108770</v>
       </c>
       <c r="B5" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>128102380</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>128108766</v>
       </c>
       <c r="B8" t="n">
-        <v>80193</v>
+        <v>80195</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,10 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128108782</v>
+        <v>128108775</v>
       </c>
       <c r="B9" t="n">
-        <v>82946</v>
+        <v>91462</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1419,21 +1419,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493906</v>
+        <v>493958</v>
       </c>
       <c r="R9" t="n">
-        <v>6933571</v>
+        <v>6933370</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128108775</v>
+        <v>128108782</v>
       </c>
       <c r="B10" t="n">
-        <v>91460</v>
+        <v>82948</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493958</v>
+        <v>493906</v>
       </c>
       <c r="R10" t="n">
-        <v>6933370</v>
+        <v>6933571</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1605,7 +1605,7 @@
         <v>128108776</v>
       </c>
       <c r="B11" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>128108778</v>
       </c>
       <c r="B12" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>128108781</v>
       </c>
       <c r="B13" t="n">
-        <v>82946</v>
+        <v>82948</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>128108777</v>
       </c>
       <c r="B14" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 26957-2024 artfynd.xlsx
+++ b/artfynd/A 26957-2024 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128103036</v>
       </c>
       <c r="B3" t="n">
-        <v>57689</v>
+        <v>57736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26957-2024 artfynd.xlsx
+++ b/artfynd/A 26957-2024 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128103036</v>
       </c>
       <c r="B3" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26957-2024 artfynd.xlsx
+++ b/artfynd/A 26957-2024 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128103036</v>
       </c>
       <c r="B3" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
